--- a/tests/testthat/fixtures/ses_2019_sa_sample.xlsx
+++ b/tests/testthat/fixtures/ses_2019_sa_sample.xlsx
@@ -1,515 +1,884 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <bookViews>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+  </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">לוח ג -</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">אזורים סטטיסטיים בתוך עיריות ומועצות</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STATISTICAL AREAS WITHIN MUNICIPALITIES AND LOCAL</t>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>לוח ג -</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>אזורים סטטיסטיים בתוך עיריות ומועצות</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>x.1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>STATISTICAL AREAS WITHIN MUNICIPALITIES AND LOCAL</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>x.2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>x.3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>x.4</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">מקומיות, לפי סדר אלף-ביתי של שמות</t>
+          <t>מקומיות, לפי סדר אלף-ביתי של שמות</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">COUNCILS, BY NAME OF LOCALITY IN HEBREW</t>
+          <t>COUNCILS, BY NAME OF LOCALITY IN HEBREW</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">היישובים, ובתוך כל יישוב - לפי סדר עולה</t>
+          <t>היישובים, ובתוך כל יישוב - לפי סדר עולה</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALPHABETICAL ORDER, AND WITHIN EACH LOCALITY -</t>
+          <t>ALPHABETICAL ORDER, AND WITHIN EACH LOCALITY -</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">של המדד החברתי-כלכלי 2019:</t>
+          <t>של המדד החברתי-כלכלי 2019:</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN ASCENDING ORDER OF THE SOCIO-ECONOMIC INDEX 2019:</t>
+          <t>IN ASCENDING ORDER OF THE SOCIO-ECONOMIC INDEX 2019:</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ערך מדד, דירוג ואשכול, ושינויים לעומת 2017</t>
+          <t>ערך מדד, דירוג ואשכול, ושינויים לעומת 2017</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">INDEX VALUE, RANK AND CLUSTER, AND CHANGES COMPARED TO 2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
+          <t>INDEX VALUE, RANK AND CLUSTER, AND CHANGES COMPARED TO 2017</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">עירייה או מועצה מקומית</t>
+          <t>עירייה או מועצה מקומית</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">אזור סטטיסטי בתוך עירייה או מועצה מקומית</t>
+          <t>אזור סטטיסטי בתוך עירייה או מועצה מקומית</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MUNICIPALITY OR LOCAL COUNCIL</t>
+          <t>MUNICIPALITY OR LOCAL COUNCIL</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">STATISTICAL AREA WITHIN MUNICIPALITY OR LOCAL COUNCIL</t>
+          <t>STATISTICAL AREA WITHIN MUNICIPALITY OR LOCAL COUNCIL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">מעמד מוניציפלי</t>
+          <t>מעמד מוניציפלי</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">סמל יישוב</t>
+          <t>סמל יישוב</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">שם יישוב</t>
+          <t>שם יישוב</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAME OF LOCALITY</t>
+          <t>NAME OF LOCALITY</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">אשכול 2019[4]</t>
+          <t>אשכול 2019[4]</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">אשכול 2017[4]</t>
+          <t>אשכול 2017[4]</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">סמל אזור סטטיסטי</t>
+          <t>סמל אזור סטטיסטי</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">אוכלוסיית המדד 2019[1]</t>
+          <t>אוכלוסיית המדד 2019[1]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">MUNICIPAL STATUS</t>
+          <t>MUNICIPAL STATUS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CODE OF LOCALITY</t>
+          <t>CODE OF LOCALITY</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLUSTER 2019[4]</t>
+          <t>CLUSTER 2019[4]</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLUSTER 2017[4]</t>
+          <t>CLUSTER 2017[4]</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CODE OF STATISTICAL AREA</t>
+          <t>CODE OF STATISTICAL AREA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">INDEX POPULATION 2019[1]</t>
+          <t>INDEX POPULATION 2019[1]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">אופקים</t>
+          <t>אופקים</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">OFAQIM</t>
+          <t>OFAQIM</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6123.0347005038002</t>
+          <t>6123.0347005038002</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">אופקים</t>
+          <t>אופקים</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">OFAQIM</t>
+          <t>OFAQIM</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3044.8290533402301</t>
+          <t>3044.8290533402301</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">אופקים</t>
+          <t>אופקים</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">OFAQIM</t>
+          <t>OFAQIM</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">3043.84559698877</t>
+          <t>3043.84559698877</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">אופקים</t>
+          <t>אופקים</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">OFAQIM</t>
+          <t>OFAQIM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2773.0505771400299</t>
+          <t>2773.0505771400299</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">אופקים</t>
+          <t>אופקים</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">OFAQIM</t>
+          <t>OFAQIM</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5246.1515117408599</t>
+          <t>5246.1515117408599</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">אופקים</t>
+          <t>אופקים</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">OFAQIM</t>
+          <t>OFAQIM</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">10424.445121802901</t>
+          <t>10424.445121802901</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2400</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">אור יהודה</t>
+          <t>אור יהודה</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">OR YEHUDA</t>
+          <t>OR YEHUDA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">219.76994277451101</t>
+          <t>219.76994277451101</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2400</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">אור יהודה</t>
+          <t>אור יהודה</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">OR YEHUDA</t>
+          <t>OR YEHUDA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023.3871398214601</t>
+          <t>2023.3871398214601</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>